--- a/engine/fertiglobe_study/Fertiglobe_Valuation_Model_09-08-2026.xlsx
+++ b/engine/fertiglobe_study/Fertiglobe_Valuation_Model_09-08-2026.xlsx
@@ -3098,111 +3098,111 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>10.11%</t>
         </is>
       </c>
       <c r="B6" s="50" t="n">
-        <v>2.812065155034444</v>
+        <v>1.881294606262658</v>
       </c>
       <c r="C6" s="50" t="n">
-        <v>2.916272155493597</v>
+        <v>1.906231159388359</v>
       </c>
       <c r="D6" s="50" t="n">
-        <v>3.039862226339971</v>
+        <v>1.933710874822986</v>
       </c>
       <c r="E6" s="50" t="n">
-        <v>3.189129586741567</v>
+        <v>1.96423507345367</v>
       </c>
       <c r="F6" s="50" t="n">
-        <v>3.373424454404759</v>
+        <v>1.998446106906989</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>7.62%</t>
+          <t>10.61%</t>
         </is>
       </c>
       <c r="B7" s="50" t="n">
-        <v>2.625256454073797</v>
+        <v>1.799321864278583</v>
       </c>
       <c r="C7" s="50" t="n">
-        <v>2.707101930204153</v>
+        <v>1.819200136998261</v>
       </c>
       <c r="D7" s="50" t="n">
-        <v>2.802638590035277</v>
+        <v>1.840893082283979</v>
       </c>
       <c r="E7" s="50" t="n">
-        <v>2.915878105995585</v>
+        <v>1.864736361713828</v>
       </c>
       <c r="F7" s="50" t="n">
-        <v>3.052569085202049</v>
+        <v>1.891153859920328</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>8.12%</t>
+          <t>11.11%</t>
         </is>
       </c>
       <c r="B8" s="50" t="n">
-        <v>2.464452484101901</v>
+        <v>1.725310865119988</v>
       </c>
       <c r="C8" s="50" t="n">
-        <v>2.529258670808904</v>
+        <v>1.741059992655157</v>
       </c>
       <c r="D8" s="50" t="n">
-        <v>2.603863873379266</v>
+        <v>1.758077165652249</v>
       </c>
       <c r="E8" s="50" t="n">
-        <v>2.690883834090796</v>
+        <v>1.776583313744466</v>
       </c>
       <c r="F8" s="50" t="n">
-        <v>2.793956218176023</v>
+        <v>1.796853853962693</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>8.62%</t>
+          <t>11.61%</t>
         </is>
       </c>
       <c r="B9" s="50" t="n">
-        <v>2.324536216041114</v>
+        <v>1.658137467034927</v>
       </c>
       <c r="C9" s="50" t="n">
-        <v>2.376144968421593</v>
+        <v>1.670493333842173</v>
       </c>
       <c r="D9" s="50" t="n">
-        <v>2.434828806720129</v>
+        <v>1.683703984752268</v>
       </c>
       <c r="E9" s="50" t="n">
-        <v>2.502322031642603</v>
+        <v>1.697910173087579</v>
       </c>
       <c r="F9" s="50" t="n">
-        <v>2.580976214546299</v>
+        <v>1.713285349820331</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>9.12%</t>
+          <t>12.11%</t>
         </is>
       </c>
       <c r="B10" s="50" t="n">
-        <v>2.20165104894726</v>
+        <v>1.596879881893651</v>
       </c>
       <c r="C10" s="50" t="n">
-        <v>2.242895136456699</v>
+        <v>1.606431083745876</v>
       </c>
       <c r="D10" s="50" t="n">
-        <v>2.289270737560642</v>
+        <v>1.616522818055062</v>
       </c>
       <c r="E10" s="50" t="n">
-        <v>2.341940712729337</v>
+        <v>1.627239460534633</v>
       </c>
       <c r="F10" s="50" t="n">
-        <v>2.402447988438872</v>
+        <v>1.638683911906381</v>
       </c>
     </row>
     <row r="11"/>
@@ -3237,19 +3237,19 @@
         </is>
       </c>
       <c r="B14" s="50" t="n">
-        <v>4.463343908513368</v>
+        <v>2.994183817038548</v>
       </c>
       <c r="C14" s="50" t="n">
-        <v>3.431462319105135</v>
+        <v>2.308550929968407</v>
       </c>
       <c r="D14" s="50" t="n">
-        <v>2.603863873379266</v>
+        <v>1.758077165652249</v>
       </c>
       <c r="E14" s="50" t="n">
-        <v>1.905609249482754</v>
+        <v>1.292892761630007</v>
       </c>
       <c r="F14" s="50" t="n">
-        <v>0.9272949341941398</v>
+        <v>0.6384482712559816</v>
       </c>
       <c r="G14" s="9">
         <f>MAX(B14:F14)-MIN(B14:F14)</f>
@@ -3263,19 +3263,19 @@
         </is>
       </c>
       <c r="B15" s="50" t="n">
-        <v>1.539215307927669</v>
+        <v>1.040893907127228</v>
       </c>
       <c r="C15" s="50" t="n">
-        <v>2.068188921125845</v>
+        <v>1.397534680906748</v>
       </c>
       <c r="D15" s="50" t="n">
-        <v>2.603863873379266</v>
+        <v>1.758077165652249</v>
       </c>
       <c r="E15" s="50" t="n">
-        <v>3.143787425516914</v>
+        <v>2.121093306576268</v>
       </c>
       <c r="F15" s="50" t="n">
-        <v>3.686575575607657</v>
+        <v>2.485777298231993</v>
       </c>
       <c r="G15" s="9">
         <f>MAX(B15:F15)-MIN(B15:F15)</f>
@@ -3285,23 +3285,23 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Beta  (0.289 / 0.400 / 0.492 / 0.600 / 0.694)</t>
+          <t>Beta  (0.465 / 0.400 / 0.931 / 0.600 / 1.398)</t>
         </is>
       </c>
       <c r="B16" s="50" t="n">
-        <v>3.347319622495193</v>
+        <v>2.68195611778392</v>
       </c>
       <c r="C16" s="50" t="n">
         <v>2.895743194908991</v>
       </c>
       <c r="D16" s="50" t="n">
-        <v>2.603863873379266</v>
+        <v>1.758077165652249</v>
       </c>
       <c r="E16" s="50" t="n">
         <v>2.328545158584609</v>
       </c>
       <c r="F16" s="50" t="n">
-        <v>2.132403938828431</v>
+        <v>1.303297041943587</v>
       </c>
       <c r="G16" s="9">
         <f>MAX(B16:F16)-MIN(B16:F16)</f>
@@ -3315,19 +3315,19 @@
         </is>
       </c>
       <c r="B17" s="50" t="n">
-        <v>2.780402641817803</v>
+        <v>1.879004164851278</v>
       </c>
       <c r="C17" s="50" t="n">
-        <v>2.677299185804137</v>
+        <v>1.80838490614347</v>
       </c>
       <c r="D17" s="50" t="n">
-        <v>2.603863873379266</v>
+        <v>1.758077165652249</v>
       </c>
       <c r="E17" s="50" t="n">
-        <v>2.505795963078508</v>
+        <v>1.690881695102874</v>
       </c>
       <c r="F17" s="50" t="n">
-        <v>2.368927379052513</v>
+        <v>1.597073587204917</v>
       </c>
       <c r="G17" s="9">
         <f>MAX(B17:F17)-MIN(B17:F17)</f>
@@ -3341,19 +3341,19 @@
         </is>
       </c>
       <c r="B18" s="50" t="n">
-        <v>2.464452484101901</v>
+        <v>1.725310865119988</v>
       </c>
       <c r="C18" s="50" t="n">
-        <v>2.529258670808904</v>
+        <v>1.741059992655157</v>
       </c>
       <c r="D18" s="50" t="n">
-        <v>2.603863873379266</v>
+        <v>1.758077165652249</v>
       </c>
       <c r="E18" s="50" t="n">
-        <v>2.690883834090796</v>
+        <v>1.776583313744466</v>
       </c>
       <c r="F18" s="50" t="n">
-        <v>2.793956218176023</v>
+        <v>1.796853853962693</v>
       </c>
       <c r="G18" s="9">
         <f>MAX(B18:F18)-MIN(B18:F18)</f>
@@ -6023,7 +6023,7 @@
         </is>
       </c>
       <c r="C64" s="32" t="n">
-        <v>0.492</v>
+        <v>0.931</v>
       </c>
     </row>
     <row r="65">

--- a/engine/fertiglobe_study/Fertiglobe_Valuation_Model_09-08-2026.xlsx
+++ b/engine/fertiglobe_study/Fertiglobe_Valuation_Model_09-08-2026.xlsx
@@ -946,7 +946,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>3.6725 dirhams to the dollar only at the last step. Market price AED 2.54 at the 2026-08-07 close.</t>
+          <t>3.6725 dirhams to the dollar only at the last step. Market price AED 2.67 at the 2026-08-07 close.</t>
         </is>
       </c>
     </row>
@@ -3101,19 +3101,19 @@
         </is>
       </c>
       <c r="B6" s="49" t="n">
-        <v>1.994253312995301</v>
+        <v>1.993072828331594</v>
       </c>
       <c r="C6" s="49" t="n">
-        <v>1.984631620481272</v>
+        <v>1.983456933682448</v>
       </c>
       <c r="D6" s="49" t="n">
-        <v>1.97407795325518</v>
+        <v>1.972909625913021</v>
       </c>
       <c r="E6" s="49" t="n">
-        <v>1.962495235702308</v>
+        <v>1.961333887904676</v>
       </c>
       <c r="F6" s="49" t="n">
-        <v>1.949772425251411</v>
+        <v>1.948618743998498</v>
       </c>
     </row>
     <row r="7">
@@ -3123,19 +3123,19 @@
         </is>
       </c>
       <c r="B7" s="49" t="n">
-        <v>1.897152412635113</v>
+        <v>1.896032093115478</v>
       </c>
       <c r="C7" s="49" t="n">
-        <v>1.885937417660905</v>
+        <v>1.884823843938417</v>
       </c>
       <c r="D7" s="49" t="n">
-        <v>1.873751267593325</v>
+        <v>1.87264502381584</v>
       </c>
       <c r="E7" s="49" t="n">
-        <v>1.860499253455257</v>
+        <v>1.859400980737891</v>
       </c>
       <c r="F7" s="49" t="n">
-        <v>1.846073937548967</v>
+        <v>1.844984341630396</v>
       </c>
     </row>
     <row r="8">
@@ -3145,19 +3145,19 @@
         </is>
       </c>
       <c r="B8" s="49" t="n">
-        <v>1.810535673563454</v>
+        <v>1.809469008452576</v>
       </c>
       <c r="C8" s="49" t="n">
-        <v>1.798197457167325</v>
+        <v>1.797138200146791</v>
       </c>
       <c r="D8" s="49" t="n">
-        <v>1.784881283585974</v>
+        <v>1.783830021839129</v>
       </c>
       <c r="E8" s="49" t="n">
-        <v>1.770497495249912</v>
+        <v>1.769454869792144</v>
       </c>
       <c r="F8" s="49" t="n">
-        <v>1.754945129561518</v>
+        <v>1.753911842027999</v>
       </c>
     </row>
     <row r="9">
@@ -3167,19 +3167,19 @@
         </is>
       </c>
       <c r="B9" s="49" t="n">
-        <v>1.732768442099322</v>
+        <v>1.731749935634973</v>
       </c>
       <c r="C9" s="49" t="n">
-        <v>1.719657364941186</v>
+        <v>1.718646716513573</v>
       </c>
       <c r="D9" s="49" t="n">
-        <v>1.705581860372723</v>
+        <v>1.704579648004987</v>
       </c>
       <c r="E9" s="49" t="n">
-        <v>1.690458509705353</v>
+        <v>1.689465361417073</v>
       </c>
       <c r="F9" s="49" t="n">
-        <v>1.674193988178525</v>
+        <v>1.673210587922852</v>
       </c>
     </row>
     <row r="10">
@@ -3189,19 +3189,19 @@
         </is>
       </c>
       <c r="B10" s="49" t="n">
-        <v>1.662539427639168</v>
+        <v>1.661564398258687</v>
       </c>
       <c r="C10" s="49" t="n">
-        <v>1.64891879066338</v>
+        <v>1.647951910145248</v>
       </c>
       <c r="D10" s="49" t="n">
-        <v>1.634359786513412</v>
+        <v>1.633401616257581</v>
       </c>
       <c r="E10" s="49" t="n">
-        <v>1.618785593556269</v>
+        <v>1.617836740923015</v>
       </c>
       <c r="F10" s="49" t="n">
-        <v>1.6021107693261</v>
+        <v>1.601171892793641</v>
       </c>
     </row>
     <row r="11"/>
@@ -3236,19 +3236,19 @@
         </is>
       </c>
       <c r="B14" s="49" t="n">
-        <v>3.068588315302267</v>
+        <v>3.066814294579432</v>
       </c>
       <c r="C14" s="49" t="n">
-        <v>2.373080187426109</v>
+        <v>2.371697224725087</v>
       </c>
       <c r="D14" s="49" t="n">
-        <v>1.810535673563454</v>
+        <v>1.809469008452576</v>
       </c>
       <c r="E14" s="49" t="n">
-        <v>1.329817995611873</v>
+        <v>1.329021619943569</v>
       </c>
       <c r="F14" s="49" t="n">
-        <v>0.6343098677357158</v>
+        <v>0.6339045500892233</v>
       </c>
       <c r="G14" s="19">
         <f>MAX(B14:F14)-MIN(B14:F14)</f>
@@ -3262,19 +3262,19 @@
         </is>
       </c>
       <c r="B15" s="49" t="n">
-        <v>1.073721004417648</v>
+        <v>1.07306192362054</v>
       </c>
       <c r="C15" s="49" t="n">
-        <v>1.442128338990551</v>
+        <v>1.441265466036558</v>
       </c>
       <c r="D15" s="49" t="n">
-        <v>1.810535673563454</v>
+        <v>1.809469008452576</v>
       </c>
       <c r="E15" s="49" t="n">
-        <v>2.178943008136358</v>
+        <v>2.177672550868594</v>
       </c>
       <c r="F15" s="49" t="n">
-        <v>2.547350342709262</v>
+        <v>2.545876093284613</v>
       </c>
       <c r="G15" s="19">
         <f>MAX(B15:F15)-MIN(B15:F15)</f>
@@ -3288,19 +3288,19 @@
         </is>
       </c>
       <c r="B16" s="49" t="n">
-        <v>2.775623423257351</v>
+        <v>2.774798551696315</v>
       </c>
       <c r="C16" s="49" t="n">
-        <v>2.999230551564709</v>
+        <v>2.998466906570427</v>
       </c>
       <c r="D16" s="49" t="n">
-        <v>1.810535673563454</v>
+        <v>1.809469008452576</v>
       </c>
       <c r="E16" s="49" t="n">
-        <v>2.406165356345159</v>
+        <v>2.405242605845986</v>
       </c>
       <c r="F16" s="49" t="n">
-        <v>1.336849722458352</v>
+        <v>1.335692487366696</v>
       </c>
       <c r="G16" s="19">
         <f>MAX(B16:F16)-MIN(B16:F16)</f>
@@ -3314,19 +3314,19 @@
         </is>
       </c>
       <c r="B17" s="49" t="n">
-        <v>1.93448979261854</v>
+        <v>1.933356736546298</v>
       </c>
       <c r="C17" s="49" t="n">
-        <v>1.862134152441707</v>
+        <v>1.861039850712991</v>
       </c>
       <c r="D17" s="49" t="n">
-        <v>1.810535673563454</v>
+        <v>1.809469008452576</v>
       </c>
       <c r="E17" s="49" t="n">
-        <v>1.741541418813652</v>
+        <v>1.740511707657481</v>
       </c>
       <c r="F17" s="49" t="n">
-        <v>1.645067231911208</v>
+        <v>1.644089193213072</v>
       </c>
       <c r="G17" s="19">
         <f>MAX(B17:F17)-MIN(B17:F17)</f>
@@ -3340,19 +3340,19 @@
         </is>
       </c>
       <c r="B18" s="49" t="n">
-        <v>1.810535673563454</v>
+        <v>1.809469008452576</v>
       </c>
       <c r="C18" s="49" t="n">
-        <v>1.798197457167325</v>
+        <v>1.797138200146791</v>
       </c>
       <c r="D18" s="49" t="n">
-        <v>1.784881283585974</v>
+        <v>1.783830021839129</v>
       </c>
       <c r="E18" s="49" t="n">
-        <v>1.770497495249912</v>
+        <v>1.769454869792144</v>
       </c>
       <c r="F18" s="49" t="n">
-        <v>1.754945129561518</v>
+        <v>1.753911842027999</v>
       </c>
       <c r="G18" s="19">
         <f>MAX(B18:F18)-MIN(B18:F18)</f>
@@ -5287,7 +5287,7 @@
         </is>
       </c>
       <c r="C5" s="24" t="n">
-        <v>2.54</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="6">
